--- a/input_parameters_v38.xlsx
+++ b/input_parameters_v38.xlsx
@@ -1,20 +1,56 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haukeschlesier/FFEI_copy/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haukeschlesier/FFEI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAB99CD1-631C-BF44-A228-83BE3EDF4A3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1FAF2C6-0C15-C640-89A3-17DD7DD4CCC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="solver_adj" localSheetId="0" hidden="1">Tabelle1!$K$25:$K$68</definedName>
+    <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
+    <definedName name="solver_drv" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_eng" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_lhs1" localSheetId="0" hidden="1">Tabelle1!$K$25:$K$68</definedName>
+    <definedName name="solver_lhs2" localSheetId="0" hidden="1">Tabelle1!$N$25:$N$68</definedName>
+    <definedName name="solver_lhs3" localSheetId="0" hidden="1">Tabelle1!$P$25:$P$68</definedName>
+    <definedName name="solver_lin" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_mni" localSheetId="0" hidden="1">30</definedName>
+    <definedName name="solver_mrt" localSheetId="0" hidden="1">0.075</definedName>
+    <definedName name="solver_msl" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_neg" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_num" localSheetId="0" hidden="1">3</definedName>
+    <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
+    <definedName name="solver_rbv" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rel1" localSheetId="0" hidden="1">3</definedName>
+    <definedName name="solver_rel2" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_rel3" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_rhs1" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_rhs2" localSheetId="0" hidden="1">Tabelle1!$O$25:$O$68</definedName>
+    <definedName name="solver_rhs3" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_rsd" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_scl" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_sho" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_ssz" localSheetId="0" hidden="1">100</definedName>
+    <definedName name="solver_tim" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_tol" localSheetId="0" hidden="1">0.01</definedName>
+    <definedName name="solver_typ" localSheetId="0" hidden="1">3</definedName>
+    <definedName name="solver_val" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_ver" localSheetId="0" hidden="1">2</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -792,7 +828,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="89">
   <si>
     <t>electricity_location</t>
   </si>
@@ -1040,10 +1076,25 @@
     <t>string of country codes; location of new transport markets</t>
   </si>
   <si>
-    <t>ecoinvent-3.8-cutoff_fossilfree_im</t>
-  </si>
-  <si>
     <t>synfuel_share</t>
+  </si>
+  <si>
+    <t>ecoinvent-3.8-cutoff_fossilfree</t>
+  </si>
+  <si>
+    <t>electrolysis_efficiency</t>
+  </si>
+  <si>
+    <t>fuel_cell_efficiency</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/article/pii/S0360319923063358</t>
+  </si>
+  <si>
+    <t>systems efficiency of fuel cell, https://onlinelibrary.wiley.com/doi/full/10.1155/2024/7271748</t>
+  </si>
+  <si>
+    <t>hydrogen; water splitting electrical-to-chemical efficiency, 1 would 100% efficiency.</t>
   </si>
 </sst>
 </file>
@@ -1903,7 +1954,7 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" s="17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B38" s="2">
         <v>0.9</v>
@@ -1920,7 +1971,7 @@
         <v>70</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>71</v>
@@ -2054,6 +2105,31 @@
       </c>
       <c r="C52" s="16" t="s">
         <v>46</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A53" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B53" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D53" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A54" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B54" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.2">
